--- a/src/test/resources/testdata/ui/pagecases.xlsx
+++ b/src/test/resources/testdata/ui/pagecases.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7455"/>
+    <workbookView windowWidth="19200" windowHeight="8055" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="testSearch" sheetId="2" r:id="rId1"/>
+    <sheet name="testCreateContract" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>查询条件</t>
   </si>
@@ -38,6 +39,22 @@
     <t>{
     "合同名称": "测试",
     "合同编号": "2020260224000036113"
+}</t>
+  </si>
+  <si>
+    <t>输入</t>
+  </si>
+  <si>
+    <t>{
+    "业务类型": "默认配置",
+    "合同标题": "测试111",
+    "添加文件": "C:\\Users\\ww\\Desktop\\测试.pdf",
+    "添加内部员工": "王耀宇"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "合同名称": "测试111"
 }</t>
   </si>
 </sst>
@@ -1008,4 +1025,36 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="51.1769911504425" customWidth="1"/>
+    <col min="2" max="2" width="37.3716814159292" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" ht="81" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/src/test/resources/testdata/ui/pagecases.xlsx
+++ b/src/test/resources/testdata/ui/pagecases.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8055" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8055" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="testSearch" sheetId="2" r:id="rId1"/>
     <sheet name="testCreateContract" sheetId="3" r:id="rId2"/>
+    <sheet name="testSignContract" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t>查询条件</t>
   </si>
@@ -55,6 +56,12 @@
   <si>
     <t>{
     "合同名称": "测试111"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "合同状态": "需要我签署",
+    "合同名称": "测试"
 }</t>
   </si>
 </sst>
@@ -1057,4 +1064,36 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="40.1592920353982" customWidth="1"/>
+    <col min="2" max="2" width="37.3716814159292" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" ht="54" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>